--- a/reports/APM_Report.xlsx
+++ b/reports/APM_Report.xlsx
@@ -486,9 +486,9 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="39" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -547,7 +547,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -562,13 +562,15 @@
           <t>Throughput</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Total Monitored Requests</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>375</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -577,12 +579,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Throughput: 39.62 req/s</t>
+          <t>Throughput: 22.38 req/s</t>
         </is>
       </c>
     </row>
@@ -597,22 +599,24 @@
           <t>Successful Requests</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>375</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>345 (92.00%)</t>
+        </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Success Rate: 100.00%</t>
+          <t>Success Rate: 92.00%</t>
         </is>
       </c>
     </row>
@@ -627,22 +631,24 @@
           <t>Failed Requests</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30 (8.00%)</t>
+        </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Error Rate: 0.00%</t>
+          <t>Error Rate: 8.00%</t>
         </is>
       </c>
     </row>
@@ -659,7 +665,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>125.98 ms</t>
+          <t>220.06 ms</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -667,9 +673,9 @@
           <t>&lt; 200 ms</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -691,7 +697,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18.8 ms</t>
+          <t>41.7 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -701,7 +707,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -723,7 +729,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32.88 ms</t>
+          <t>99.32 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -733,7 +739,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -755,7 +761,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48.69 ms</t>
+          <t>2048.1 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -763,9 +769,9 @@
           <t>&lt; 500 ms</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -787,7 +793,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2565.91 ms</t>
+          <t>2520.67 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -795,9 +801,9 @@
           <t>&lt; 1000 ms</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -819,7 +825,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3051.21 ms</t>
+          <t>2952.82 ms</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -827,9 +833,9 @@
           <t>&lt; 2000 ms</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -851,7 +857,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63.65%</t>
+          <t>56.38%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -861,7 +867,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -883,22 +889,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59.18 MB</t>
+          <t>59.13 MB</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Growth &lt; 100 MB</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 59.19 MB (+0.54 MB growth)</t>
+          <t>Max RAM: 59.16 MB (+0.71 MB growth)</t>
         </is>
       </c>
     </row>
@@ -925,12 +931,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ping: 1.9 ms (mysql)</t>
+          <t>Ping: 2.0 ms (sqlite)</t>
         </is>
       </c>
     </row>
@@ -945,19 +951,19 @@
           <t>APM Execution Evaluation</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>🟢 PASS</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>APM TESTING FAILED</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>PASS / WARNING</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>APM TESTING PASSED</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>APM TESTING FAILED</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1087,20 +1093,20 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.94</v>
+        <v>26.23</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>12.69</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35.88</v>
+        <v>47</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1135,20 +1141,20 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>14.19</v>
+        <v>30.57</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.99</v>
+        <v>63.08</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1183,20 +1189,20 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>13.24</v>
+        <v>57.49</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9.26</v>
+        <v>26.46</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.35</v>
+        <v>75.86</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1231,20 +1237,20 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.79</v>
+        <v>92.97</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.34</v>
+        <v>62.2</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>85.2</v>
+        <v>158.12</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1279,20 +1285,20 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.15</v>
+        <v>44.23</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10.77</v>
+        <v>22</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>45.68</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4.75</v>
+        <v>2.69</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1327,20 +1333,20 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13.26</v>
+        <v>33.22</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17.5</v>
+        <v>42.01</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1375,20 +1381,20 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>21.11</v>
+        <v>38.62</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10.34</v>
+        <v>29.25</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29.17</v>
+        <v>47.53</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1423,20 +1429,20 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>21.44</v>
+        <v>65.45</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.06</v>
+        <v>49.66</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.19</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1471,20 +1477,20 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17.36</v>
+        <v>41.71</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.01</v>
+        <v>22.39</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21.94</v>
+        <v>49.83</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1519,20 +1525,20 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>18.28</v>
+        <v>46.55</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10.66</v>
+        <v>37.15</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22.9</v>
+        <v>58.27</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1567,20 +1573,20 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.2</v>
+        <v>39.03</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.79</v>
+        <v>17.38</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.07</v>
+        <v>50.19</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1615,20 +1621,20 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17.73</v>
+        <v>36.04</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.09</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21.04</v>
+        <v>43.54</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1663,20 +1669,20 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.81</v>
+        <v>33.81</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.2</v>
+        <v>19.16</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24.43</v>
+        <v>43.09</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1711,20 +1717,20 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>17.52</v>
+        <v>36.29</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11.67</v>
+        <v>21.85</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21.7</v>
+        <v>47.12</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1759,20 +1765,20 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>20.84</v>
+        <v>53.84</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.17</v>
+        <v>44.02</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32.9</v>
+        <v>66.64</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1807,20 +1813,20 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>18.06</v>
+        <v>49.28</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13.46</v>
+        <v>40.48</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22.54</v>
+        <v>56.28</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1855,20 +1861,20 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>18.38</v>
+        <v>42.08</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14.87</v>
+        <v>33.88</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23.1</v>
+        <v>50.46</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1903,20 +1909,20 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20.84</v>
+        <v>39.2</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.63</v>
+        <v>30.37</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>25.94</v>
+        <v>52.07</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1951,20 +1957,20 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>18.04</v>
+        <v>36.1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.42</v>
+        <v>29.05</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22.04</v>
+        <v>43.29</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -1999,20 +2005,20 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>13.66</v>
+        <v>31.68</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
+        <v>22.77</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21.71</v>
+        <v>39.47</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -2047,20 +2053,20 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.93</v>
+        <v>138.93</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.8</v>
+        <v>30.75</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>554.2</v>
+        <v>1602.92</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.58</v>
+        <v>0.9</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -2084,31 +2090,31 @@
         <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2481.1</v>
+        <v>2351.61</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1027.71</v>
+        <v>1346.97</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3051.21</v>
+        <v>2952.82</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>0.9</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -2132,31 +2138,31 @@
         <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>190.35</v>
+        <v>2048.16</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.06</v>
+        <v>2037.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2405.45</v>
+        <v>2067.2</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>0.9</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2235,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tr-f6134f142fa2</t>
+          <t>tr-ba968fe450f4</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2244,16 +2250,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.343</t>
+          <t>17:47:52.451</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.359</t>
+          <t>17:47:52.464</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.75</v>
+        <v>12.69</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>200</v>
@@ -2267,7 +2273,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tr-f64f3c0c26e2</t>
+          <t>tr-c1935fa659bf</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2282,16 +2288,16 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.343</t>
+          <t>17:47:52.459</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.369</t>
+          <t>17:47:52.480</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>25.97</v>
+        <v>21.19</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>200</v>
@@ -2305,7 +2311,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tr-005013e85f46</t>
+          <t>tr-bd26493c42e6</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2320,16 +2326,16 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.344</t>
+          <t>17:47:52.464</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.372</t>
+          <t>17:47:52.480</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.64</v>
+        <v>16.65</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>200</v>
@@ -2343,7 +2349,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tr-7ea8e2bdf774</t>
+          <t>tr-3a17b6c343fc</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2358,16 +2364,16 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.345</t>
+          <t>17:47:52.468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.381</t>
+          <t>17:47:52.486</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35.88</v>
+        <v>18.62</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>200</v>
@@ -2381,7 +2387,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tr-9177de292ac3</t>
+          <t>tr-e5d9ef842a11</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2396,16 +2402,16 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.349</t>
+          <t>17:47:52.480</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.375</t>
+          <t>17:47:52.494</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>26.69</v>
+        <v>14.07</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>200</v>
@@ -2419,7 +2425,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tr-c22d16dda8ef</t>
+          <t>tr-0e8b1b3b7bdc</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2434,16 +2440,16 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.359</t>
+          <t>17:47:52.487</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.375</t>
+          <t>17:47:52.506</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>15.6</v>
+        <v>18.46</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>200</v>
@@ -2457,7 +2463,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>tr-f7db73cce5d5</t>
+          <t>tr-67d5db46b21a</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2472,16 +2478,16 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.369</t>
+          <t>17:47:52.487</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.378</t>
+          <t>17:47:52.509</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>21.18</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>200</v>
@@ -2495,7 +2501,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tr-5e313f029a81</t>
+          <t>tr-bd5f979ddf67</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2510,16 +2516,16 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.372</t>
+          <t>17:47:52.492</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.380</t>
+          <t>17:47:52.519</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>26.28</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>200</v>
@@ -2533,7 +2539,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tr-faa0f7563349</t>
+          <t>tr-204bc21d23a1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2548,16 +2554,16 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.375</t>
+          <t>17:47:52.494</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.385</t>
+          <t>17:47:52.517</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.15</v>
+        <v>23</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>200</v>
@@ -2571,7 +2577,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>tr-9044d6dd934f</t>
+          <t>tr-53824dd8c9ff</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2586,16 +2592,16 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.375</t>
+          <t>17:47:52.598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.389</t>
+          <t>17:47:52.645</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>14.1</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>200</v>
@@ -2609,7 +2615,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>tr-f1b9faa19cae</t>
+          <t>tr-40602f87ab43</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2624,16 +2630,16 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.378</t>
+          <t>17:47:52.608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.390</t>
+          <t>17:47:52.637</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.72</v>
+        <v>29</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>200</v>
@@ -2647,7 +2653,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tr-14b1c5e852dc</t>
+          <t>tr-e12d0a32934a</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2662,16 +2668,16 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.380</t>
+          <t>17:47:52.608</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.393</t>
+          <t>17:47:52.651</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>12.87</v>
+        <v>42.83</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>200</v>
@@ -2685,7 +2691,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tr-9a87ba679a49</t>
+          <t>tr-e17b59593b74</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2700,16 +2706,16 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.382</t>
+          <t>17:47:52.610</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.396</t>
+          <t>17:47:52.652</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13.41</v>
+        <v>41.84</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>200</v>
@@ -2723,7 +2729,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tr-0da6a2bc411c</t>
+          <t>tr-1f9f6967ce54</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2738,16 +2744,16 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.385</t>
+          <t>17:47:52.611</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.397</t>
+          <t>17:47:52.648</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>11.83</v>
+        <v>36.83</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>200</v>
@@ -2761,7 +2767,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tr-f4df794678ba</t>
+          <t>tr-894ff1e3ffc6</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2776,16 +2782,16 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.389</t>
+          <t>17:47:52.637</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.404</t>
+          <t>17:47:52.661</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>15.01</v>
+        <v>23.83</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>200</v>
@@ -2799,7 +2805,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tr-cdc1e8c8a9d7</t>
+          <t>tr-7767764e4db7</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2814,16 +2820,16 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.390</t>
+          <t>17:47:52.645</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.406</t>
+          <t>17:47:52.671</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>15.59</v>
+        <v>25.7</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>200</v>
@@ -2837,7 +2843,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tr-41d613724a97</t>
+          <t>tr-fe6bc9d23a3c</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2852,16 +2858,16 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.393</t>
+          <t>17:47:52.648</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.403</t>
+          <t>17:47:52.678</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10.04</v>
+        <v>30</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>200</v>
@@ -2875,7 +2881,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tr-13ea0ed70671</t>
+          <t>tr-6aa83b05d3c3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2890,16 +2896,16 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.396</t>
+          <t>17:47:52.651</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.409</t>
+          <t>17:47:52.680</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>13.47</v>
+        <v>29</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>200</v>
@@ -2913,7 +2919,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tr-1a11e394a424</t>
+          <t>tr-e3218a6c7ab4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2928,16 +2934,16 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.397</t>
+          <t>17:47:52.652</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.410</t>
+          <t>17:47:52.688</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>13.47</v>
+        <v>35.99</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>200</v>
@@ -2951,7 +2957,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tr-065f34da0560</t>
+          <t>tr-7e99025ae969</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2966,16 +2972,16 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.403</t>
+          <t>17:47:52.661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.413</t>
+          <t>17:47:52.696</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>35</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>200</v>
@@ -2989,7 +2995,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>tr-a4ac242191f0</t>
+          <t>tr-b547fb98b510</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3004,16 +3010,16 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.405</t>
+          <t>17:47:52.671</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.415</t>
+          <t>17:47:52.693</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>200</v>
@@ -3027,7 +3033,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>tr-d9d24fca359a</t>
+          <t>tr-97e5abb21bf2</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3042,16 +3048,16 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.406</t>
+          <t>17:47:52.679</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.416</t>
+          <t>17:47:52.702</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>9.73</v>
+        <v>22.96</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>200</v>
@@ -3065,7 +3071,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>tr-d1925934e9b1</t>
+          <t>tr-72f0516c9a26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3080,16 +3086,16 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.409</t>
+          <t>17:47:52.680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.423</t>
+          <t>17:47:52.703</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>13.99</v>
+        <v>23.13</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>200</v>
@@ -3103,7 +3109,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>tr-9fccacf7d54c</t>
+          <t>tr-a7cd4de5cb98</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3118,16 +3124,16 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.410</t>
+          <t>17:47:52.688</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.421</t>
+          <t>17:47:52.710</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>10.77</v>
+        <v>22.01</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>200</v>
@@ -3141,7 +3147,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>tr-a7f87a38f055</t>
+          <t>tr-da711b5fe730</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3156,16 +3162,16 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.413</t>
+          <t>17:47:52.693</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.430</t>
+          <t>17:47:52.724</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>17.35</v>
+        <v>31.17</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>200</v>
@@ -3179,7 +3185,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tr-0ec334c2a062</t>
+          <t>tr-eeaf58b1ea76</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3194,16 +3200,16 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.415</t>
+          <t>17:47:52.696</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.465</t>
+          <t>17:47:52.726</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>49.99</v>
+        <v>30.18</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>200</v>
@@ -3217,7 +3223,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>tr-158795e775d5</t>
+          <t>tr-2904432d6e88</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3232,16 +3238,16 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.416</t>
+          <t>17:47:52.702</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.425</t>
+          <t>17:47:52.731</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>29.61</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>200</v>
@@ -3255,7 +3261,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>tr-408d2a068cf7</t>
+          <t>tr-5b6a04da13d6</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3270,16 +3276,16 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.421</t>
+          <t>17:47:52.703</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.430</t>
+          <t>17:47:52.733</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>9.16</v>
+        <v>29.98</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>200</v>
@@ -3293,7 +3299,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>tr-124f273c6113</t>
+          <t>tr-77ebabd15120</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3308,16 +3314,16 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.423</t>
+          <t>17:47:52.710</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.433</t>
+          <t>17:47:52.739</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>28.77</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>200</v>
@@ -3331,7 +3337,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>tr-ac89f24b13f8</t>
+          <t>tr-e61bade8f661</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3346,16 +3352,16 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.425</t>
+          <t>17:47:52.724</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.436</t>
+          <t>17:47:52.787</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>11.14</v>
+        <v>63.08</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>200</v>
@@ -3369,7 +3375,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>tr-aa2467e478c1</t>
+          <t>tr-d901524241bc</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3384,16 +3390,16 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.430</t>
+          <t>17:47:52.726</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.443</t>
+          <t>17:47:52.753</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>12.82</v>
+        <v>26.46</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>200</v>
@@ -3407,7 +3413,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>tr-e1a865dfafe3</t>
+          <t>tr-dacc1a039ffb</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3422,16 +3428,16 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.430</t>
+          <t>17:47:52.731</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.439</t>
+          <t>17:47:52.768</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>9.26</v>
+        <v>37.16</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>200</v>
@@ -3445,7 +3451,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>tr-cf72dfa2fdd4</t>
+          <t>tr-544ec551ef68</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3460,16 +3466,16 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.433</t>
+          <t>17:47:52.733</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.444</t>
+          <t>17:47:52.769</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>10.98</v>
+        <v>35.86</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>200</v>
@@ -3483,7 +3489,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>tr-709aef6daecc</t>
+          <t>tr-78cb37b47e1d</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3498,16 +3504,16 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.436</t>
+          <t>17:47:52.739</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.446</t>
+          <t>17:47:52.777</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>10.57</v>
+        <v>38.09</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>200</v>
@@ -3521,7 +3527,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>tr-70c0a0c966b6</t>
+          <t>tr-c915e6367afa</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3536,16 +3542,16 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.440</t>
+          <t>17:47:52.753</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.450</t>
+          <t>17:47:52.817</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>64.37</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>200</v>
@@ -3559,7 +3565,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>tr-56c686f59e41</t>
+          <t>tr-91a0e8cd799d</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3574,16 +3580,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.443</t>
+          <t>17:47:52.769</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.458</t>
+          <t>17:47:52.833</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>14.98</v>
+        <v>63.93</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>200</v>
@@ -3597,7 +3603,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>tr-d9ba3346b222</t>
+          <t>tr-2bab15709914</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3612,16 +3618,16 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.444</t>
+          <t>17:47:52.769</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.457</t>
+          <t>17:47:52.832</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>12.96</v>
+        <v>62.6</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>200</v>
@@ -3635,7 +3641,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>tr-685ebee38623</t>
+          <t>tr-4605e174dff6</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3650,16 +3656,16 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.446</t>
+          <t>17:47:52.777</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.460</t>
+          <t>17:47:52.841</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>13.21</v>
+        <v>64.25</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>200</v>
@@ -3673,7 +3679,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>tr-970dd7b4ae24</t>
+          <t>tr-607395d5a272</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3688,16 +3694,16 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.450</t>
+          <t>17:47:52.787</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.462</t>
+          <t>17:47:52.846</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>12.46</v>
+        <v>58.32</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>200</v>
@@ -3711,7 +3717,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>tr-ab9e72c219d4</t>
+          <t>tr-5de4061e982e</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3726,16 +3732,16 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.457</t>
+          <t>17:47:52.817</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.467</t>
+          <t>17:47:52.882</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>10.17</v>
+        <v>65.02</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>200</v>
@@ -3749,7 +3755,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>tr-3bb683cc1d38</t>
+          <t>tr-715497e47a72</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3764,16 +3770,16 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.458</t>
+          <t>17:47:52.832</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.472</t>
+          <t>17:47:52.908</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>14.15</v>
+        <v>75.86</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>200</v>
@@ -3787,7 +3793,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>tr-f668d271f1f8</t>
+          <t>tr-4b7941f7407b</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3802,16 +3808,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.460</t>
+          <t>17:47:52.833</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.477</t>
+          <t>17:47:52.902</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>17.31</v>
+        <v>69.28</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>200</v>
@@ -3825,7 +3831,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>tr-459e7a08ec99</t>
+          <t>tr-cebd7c85590b</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3840,16 +3846,16 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.462</t>
+          <t>17:47:52.841</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.480</t>
+          <t>17:47:52.902</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>18.35</v>
+        <v>60.72</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>200</v>
@@ -3863,7 +3869,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>tr-03deb76e9cf9</t>
+          <t>tr-f8199c9e0c6e</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3878,16 +3884,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.465</t>
+          <t>17:47:52.846</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.479</t>
+          <t>17:47:52.916</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>13.92</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>200</v>
@@ -3901,7 +3907,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>tr-ce502c90fca9</t>
+          <t>tr-0298b492bf26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3916,16 +3922,16 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.467</t>
+          <t>17:47:52.882</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.485</t>
+          <t>17:47:52.952</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>18.01</v>
+        <v>69.81</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>200</v>
@@ -3939,7 +3945,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>tr-2454fd829a95</t>
+          <t>tr-28300329faef</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3954,16 +3960,16 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.472</t>
+          <t>17:47:52.902</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.494</t>
+          <t>17:47:53.005</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>22.02</v>
+        <v>103.36</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>200</v>
@@ -3977,7 +3983,7 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>tr-00c559a119e0</t>
+          <t>tr-9b717ca34752</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3992,16 +3998,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.477</t>
+          <t>17:47:52.902</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.508</t>
+          <t>17:47:52.981</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>31.07</v>
+        <v>78.87</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>200</v>
@@ -4015,7 +4021,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>tr-294e56979ce1</t>
+          <t>tr-4009137e5f7f</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4030,16 +4036,16 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.479</t>
+          <t>17:47:52.909</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.511</t>
+          <t>17:47:53.018</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>32.85</v>
+        <v>108.47</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>200</v>
@@ -4053,7 +4059,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>tr-cd2b50d6909a</t>
+          <t>tr-258c05c8248b</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4068,16 +4074,16 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.480</t>
+          <t>17:47:52.916</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.515</t>
+          <t>17:47:53.017</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>34.77</v>
+        <v>100.42</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>200</v>
@@ -4091,7 +4097,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>tr-250f7626ded7</t>
+          <t>tr-b3d3b48134e2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4106,16 +4112,16 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.485</t>
+          <t>17:47:52.953</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11:44:16.511</t>
+          <t>17:47:53.038</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>26.44</v>
+        <v>85.16</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>200</v>

--- a/reports/APM_Report.xlsx
+++ b/reports/APM_Report.xlsx
@@ -40,13 +40,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="00C65911"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C65911"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -65,14 +65,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -527,160 +527,160 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>App Health</t>
+          <t>Overall APM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Application Availability</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>100% (Available)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>Overall APM Evaluation</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>APM TESTING FAILED</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>APM TESTING PASSED</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>APM TESTING FAILED</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FastAPI Core Engine Status</t>
+          <t>Master APM Status Evaluation</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>App Health</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Application Availability</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>100% (Available)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI Core Engine Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Throughput</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Total Monitored Requests</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>&gt; 0</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Throughput: 22.38 req/s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Success Rate</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Successful Requests</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>345 (92.00%)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Success Rate: 92.00%</t>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Throughput: 19.91 req/s</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Success Rate</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Successful Requests</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>369 (98.40%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Success Rate: 98.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>Error Rate</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Failed Requests</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>30 (8.00%)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6 (1.60%)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Error Rate: 8.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Response Time</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Average Latency</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>220.06 ms</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>&lt; 200 ms</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Mean response duration</t>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Error Rate: 1.60%</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>P50 Latency (Median)</t>
+          <t>Average Latency</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41.7 ms</t>
+          <t>249.94 ms</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>&lt; 300 ms</t>
+          <t>&lt; 200 ms</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50th percentile latency</t>
+          <t>Mean response duration</t>
         </is>
       </c>
     </row>
@@ -724,27 +724,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>P90 Latency</t>
+          <t>P50 Latency (Median)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>99.32 ms</t>
+          <t>39.42 ms</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>&lt; 500 ms</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+          <t>&lt; 300 ms</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90th percentile latency</t>
+          <t>50th percentile latency</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>P95 Latency</t>
+          <t>P90 Latency</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2048.1 ms</t>
+          <t>80.48 ms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95th percentile latency threshold</t>
+          <t>90th percentile latency</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>P99 Latency</t>
+          <t>P95 Latency</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2520.67 ms</t>
+          <t>531.13 ms</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>&lt; 1000 ms</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+          <t>&lt; 500 ms</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99th percentile latency</t>
+          <t>95th percentile latency threshold</t>
         </is>
       </c>
     </row>
@@ -820,155 +820,155 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Maximum Latency</t>
+          <t>P99 Latency</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2952.82 ms</t>
+          <t>5032.38 ms</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>&lt; 2000 ms</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+          <t>&lt; 1000 ms</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Peak latency observed</t>
+          <t>99th percentile latency</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CPU Usage</t>
+          <t>Response Time</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Average CPU Utilization</t>
+          <t>Maximum Latency</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56.38%</t>
+          <t>5798.12 ms</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>&lt; 80.0%</t>
+          <t>&lt; 2000 ms</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Peak CPU: 100.0%</t>
+          <t>Peak latency observed</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Memory Usage</t>
+          <t>CPU Usage</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Average Memory Usage</t>
+          <t>Average CPU Utilization</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59.13 MB</t>
+          <t>62.78%</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Growth &lt; 100 MB</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+          <t>&lt; 80.0%</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Max RAM: 59.16 MB (+0.71 MB growth)</t>
+          <t>Peak CPU: 100.0%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Memory Usage</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Database Health</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>HEALTHY</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>HEALTHY</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+          <t>Average Memory Usage</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>59.02 MB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Growth &lt; 100 MB</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ping: 2.0 ms (sqlite)</t>
+          <t>Max RAM: 59.04 MB (+0.43 MB growth)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Overall APM</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>APM Execution Evaluation</t>
+          <t>Database Health</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>APM TESTING FAILED</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>APM TESTING PASSED</t>
+          <t>HEALTHY</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>HEALTHY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>APM TESTING FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Master APM Status</t>
+          <t>Ping: 12.0 ms (sqlite)</t>
         </is>
       </c>
     </row>
@@ -1093,18 +1093,18 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26.23</v>
+        <v>56.11</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.69</v>
+        <v>12.9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>47</v>
+        <v>103.48</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1141,18 +1141,18 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>30.57</v>
+        <v>60.57</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>22</v>
+        <v>41.26</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>63.08</v>
+        <v>83.17</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1189,18 +1189,18 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.49</v>
+        <v>54.56</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.46</v>
+        <v>46.91</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>75.86</v>
+        <v>71.45</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1237,18 +1237,18 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>92.97</v>
+        <v>89.38</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>62.2</v>
+        <v>67.34</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>158.12</v>
+        <v>172.23</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1285,18 +1285,18 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>44.23</v>
+        <v>81.52</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22</v>
+        <v>33.69</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>73.18000000000001</v>
+        <v>273.92</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+        <v>2.39</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1333,18 +1333,18 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>33.22</v>
+        <v>31.73</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>17.95</v>
+        <v>21.02</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42.01</v>
+        <v>39.18</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1381,18 +1381,18 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>38.62</v>
+        <v>38.72</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29.25</v>
+        <v>28.08</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>47.53</v>
+        <v>49.06</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1429,18 +1429,18 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.45</v>
+        <v>44.01</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>49.66</v>
+        <v>33.7</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80.43000000000001</v>
+        <v>56.82</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1477,18 +1477,18 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>41.71</v>
+        <v>32.13</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.39</v>
+        <v>24.48</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>49.83</v>
+        <v>36.71</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1525,18 +1525,18 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46.55</v>
+        <v>33.63</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.15</v>
+        <v>26.92</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>58.27</v>
+        <v>43.41</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1573,18 +1573,18 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>39.03</v>
+        <v>31.78</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>17.38</v>
+        <v>26.3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50.19</v>
+        <v>37.35</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1621,18 +1621,18 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>36.04</v>
+        <v>32.38</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22</v>
+        <v>29.6</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>43.54</v>
+        <v>36.48</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>33.81</v>
+        <v>32.28</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.16</v>
+        <v>26.91</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>43.09</v>
+        <v>38.26</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1717,18 +1717,18 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>36.29</v>
+        <v>37.21</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.85</v>
+        <v>31.83</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47.12</v>
+        <v>46.61</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1765,18 +1765,18 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.84</v>
+        <v>45.38</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44.02</v>
+        <v>36.55</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>66.64</v>
+        <v>51.72</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1813,18 +1813,18 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.28</v>
+        <v>43.04</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.48</v>
+        <v>39.18</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56.28</v>
+        <v>47.04</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1861,18 +1861,18 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>42.08</v>
+        <v>39.43</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.88</v>
+        <v>34.23</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>50.46</v>
+        <v>46.25</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1909,18 +1909,18 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>39.2</v>
+        <v>34.85</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.37</v>
+        <v>26.75</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>52.07</v>
+        <v>41.12</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -1957,18 +1957,18 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>36.1</v>
+        <v>34.03</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.05</v>
+        <v>26.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>43.29</v>
+        <v>42.55</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -2005,18 +2005,18 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>31.68</v>
+        <v>25.84</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.77</v>
+        <v>20.34</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39.47</v>
+        <v>30.34</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -2053,18 +2053,18 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>138.93</v>
+        <v>372.79</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.75</v>
+        <v>25</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1602.92</v>
+        <v>1747.34</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -2090,29 +2090,29 @@
         <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2351.61</v>
+        <v>4721.67</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1346.97</v>
+        <v>2993.66</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2952.82</v>
+        <v>5798.12</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
@@ -2138,31 +2138,31 @@
         <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>15</v>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2048.16</v>
+        <v>112.4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2037.5</v>
+        <v>29.24</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2067.2</v>
+        <v>1131.3</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2187,7 +2187,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2228,6 +2229,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Exception / Error Details</t>
         </is>
       </c>
@@ -2235,7 +2241,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tr-ba968fe450f4</t>
+          <t>tr-9a673ebadfda</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2250,21 +2256,26 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.451</t>
+          <t>18:06:33.425</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.464</t>
+          <t>18:06:33.449</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>12.69</v>
+        <v>24.27</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2273,7 +2284,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tr-c1935fa659bf</t>
+          <t>tr-75023566e4e5</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2288,21 +2299,26 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.459</t>
+          <t>18:06:33.426</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.480</t>
+          <t>18:06:33.454</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>21.19</v>
+        <v>27.56</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2311,7 +2327,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tr-bd26493c42e6</t>
+          <t>tr-9bfd7da06d18</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2326,21 +2342,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.464</t>
+          <t>18:06:33.431</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.480</t>
+          <t>18:06:33.457</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>16.65</v>
+        <v>25.69</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2349,7 +2370,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tr-3a17b6c343fc</t>
+          <t>tr-b87c7df16d5e</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2364,21 +2385,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.468</t>
+          <t>18:06:33.449</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.486</t>
+          <t>18:06:33.462</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>18.62</v>
+        <v>12.9</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2387,7 +2413,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tr-e5d9ef842a11</t>
+          <t>tr-7dd4e97e1046</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2402,21 +2428,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.480</t>
+          <t>18:06:33.495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.494</t>
+          <t>18:06:33.591</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>14.07</v>
+        <v>96.39</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2425,7 +2456,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tr-0e8b1b3b7bdc</t>
+          <t>tr-c729b2fe2583</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2440,21 +2471,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.487</t>
+          <t>18:06:33.495</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.506</t>
+          <t>18:06:33.568</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>18.46</v>
+        <v>72.56</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2463,7 +2499,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>tr-67d5db46b21a</t>
+          <t>tr-567f00d55eaa</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2478,21 +2514,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.487</t>
+          <t>18:06:33.497</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.509</t>
+          <t>18:06:33.567</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21.18</v>
+        <v>69.73</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2501,7 +2542,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tr-bd5f979ddf67</t>
+          <t>tr-f0395e4bccc1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2516,21 +2557,26 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.492</t>
+          <t>18:06:33.499</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.519</t>
+          <t>18:06:33.603</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26.28</v>
+        <v>103.48</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2539,7 +2585,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>tr-204bc21d23a1</t>
+          <t>tr-fecc4299966a</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2554,21 +2600,26 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.494</t>
+          <t>18:06:33.508</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.517</t>
+          <t>18:06:33.611</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>23</v>
+        <v>103.39</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2577,7 +2628,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>tr-53824dd8c9ff</t>
+          <t>tr-71039a4fc834</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2592,21 +2643,26 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.598</t>
+          <t>18:06:33.567</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.645</t>
+          <t>18:06:33.623</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>47</v>
+        <v>55.84</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2615,7 +2671,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>tr-40602f87ab43</t>
+          <t>tr-cb30b824a281</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2630,21 +2686,26 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.608</t>
+          <t>18:06:33.568</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.637</t>
+          <t>18:06:33.607</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>29</v>
+        <v>39.83</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2653,7 +2714,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>tr-e12d0a32934a</t>
+          <t>tr-1087b6d87d00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2668,21 +2729,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.608</t>
+          <t>18:06:33.591</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.651</t>
+          <t>18:06:33.650</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>42.83</v>
+        <v>58.39</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2691,7 +2757,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tr-e17b59593b74</t>
+          <t>tr-192eae3a996e</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2706,21 +2772,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.610</t>
+          <t>18:06:33.603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.652</t>
+          <t>18:06:33.646</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>41.84</v>
+        <v>43.29</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2729,7 +2800,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tr-1f9f6967ce54</t>
+          <t>tr-fd1d959ae1a7</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2744,21 +2815,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.611</t>
+          <t>18:06:33.607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.648</t>
+          <t>18:06:33.659</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>36.83</v>
+        <v>51.97</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2767,7 +2843,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tr-894ff1e3ffc6</t>
+          <t>tr-bd182fca37a6</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2782,21 +2858,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.637</t>
+          <t>18:06:33.611</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.661</t>
+          <t>18:06:33.668</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>23.83</v>
+        <v>56.35</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2805,7 +2886,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tr-7767764e4db7</t>
+          <t>tr-885267336479</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2820,21 +2901,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.645</t>
+          <t>18:06:33.623</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.671</t>
+          <t>18:06:33.675</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>25.7</v>
+        <v>51.64</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2843,7 +2929,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tr-fe6bc9d23a3c</t>
+          <t>tr-d5ece1cb7a00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2858,21 +2944,26 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.648</t>
+          <t>18:06:33.646</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.678</t>
+          <t>18:06:33.703</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>30</v>
+        <v>57.3</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2881,7 +2972,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tr-6aa83b05d3c3</t>
+          <t>tr-47178ba8e98c</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2896,21 +2987,26 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.651</t>
+          <t>18:06:33.650</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.680</t>
+          <t>18:06:33.695</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>29</v>
+        <v>45.33</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2919,7 +3015,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tr-e3218a6c7ab4</t>
+          <t>tr-266bbe1928e9</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2934,21 +3030,26 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.652</t>
+          <t>18:06:33.659</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.688</t>
+          <t>18:06:33.709</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>35.99</v>
+        <v>49.74</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2957,7 +3058,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tr-7e99025ae969</t>
+          <t>tr-ec0cdfa705ab</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2972,21 +3073,26 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.661</t>
+          <t>18:06:33.668</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.696</t>
+          <t>18:06:33.734</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>35</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -2995,7 +3101,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>tr-b547fb98b510</t>
+          <t>tr-1950a2be4f40</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3010,21 +3116,26 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.671</t>
+          <t>18:06:33.675</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.693</t>
+          <t>18:06:33.744</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>22</v>
+        <v>68.75</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3033,7 +3144,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>tr-97e5abb21bf2</t>
+          <t>tr-eea3e3f3d654</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3048,21 +3159,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.679</t>
+          <t>18:06:33.696</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.702</t>
+          <t>18:06:33.761</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>22.96</v>
+        <v>65.3</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3071,7 +3187,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>tr-72f0516c9a26</t>
+          <t>tr-2f5554507bda</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3086,21 +3202,26 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.680</t>
+          <t>18:06:33.703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.703</t>
+          <t>18:06:33.763</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>23.13</v>
+        <v>60.21</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3109,7 +3230,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>tr-a7cd4de5cb98</t>
+          <t>tr-decf804c31da</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -3124,21 +3245,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.688</t>
+          <t>18:06:33.709</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.710</t>
+          <t>18:06:33.769</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>22.01</v>
+        <v>60.15</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3147,7 +3273,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>tr-da711b5fe730</t>
+          <t>tr-9a0353c5ce0c</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3162,21 +3288,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.693</t>
+          <t>18:06:33.734</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.724</t>
+          <t>18:06:33.780</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>31.17</v>
+        <v>45.67</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3185,7 +3316,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tr-eeaf58b1ea76</t>
+          <t>tr-63eaf293d173</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -3200,21 +3331,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.696</t>
+          <t>18:06:33.744</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.726</t>
+          <t>18:06:33.800</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>30.18</v>
+        <v>55.99</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3223,7 +3359,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>tr-2904432d6e88</t>
+          <t>tr-1a95f906bd3c</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3238,21 +3374,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.702</t>
+          <t>18:06:33.761</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.731</t>
+          <t>18:06:33.803</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>29.61</v>
+        <v>41.26</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3261,7 +3402,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>tr-5b6a04da13d6</t>
+          <t>tr-2e5f35485300</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -3276,21 +3417,26 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.703</t>
+          <t>18:06:33.764</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.733</t>
+          <t>18:06:33.847</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>29.98</v>
+        <v>83.17</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3299,7 +3445,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>tr-77ebabd15120</t>
+          <t>tr-93cba296a0cc</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -3314,21 +3460,26 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.710</t>
+          <t>18:06:33.770</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.739</t>
+          <t>18:06:33.848</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>28.77</v>
+        <v>78.05</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3337,7 +3488,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>tr-e61bade8f661</t>
+          <t>tr-8af711f6d2ac</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3352,21 +3503,26 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.724</t>
+          <t>18:06:33.780</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.787</t>
+          <t>18:06:33.860</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>63.08</v>
+        <v>79.58</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3375,7 +3531,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>tr-d901524241bc</t>
+          <t>tr-1856f1c26b62</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3390,21 +3546,26 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.726</t>
+          <t>18:06:33.800</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.753</t>
+          <t>18:06:33.867</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>26.46</v>
+        <v>67.53</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3413,7 +3574,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>tr-dacc1a039ffb</t>
+          <t>tr-fd120a84350f</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3428,21 +3589,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.731</t>
+          <t>18:06:33.803</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.768</t>
+          <t>18:06:33.874</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>37.16</v>
+        <v>71.45</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3451,7 +3617,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>tr-544ec551ef68</t>
+          <t>tr-40a2308e3ba1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3466,21 +3632,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.733</t>
+          <t>18:06:33.847</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.769</t>
+          <t>18:06:33.898</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>35.86</v>
+        <v>50.27</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3489,7 +3660,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>tr-78cb37b47e1d</t>
+          <t>tr-8828360fb312</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3504,21 +3675,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.739</t>
+          <t>18:06:33.848</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.777</t>
+          <t>18:06:33.898</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>38.09</v>
+        <v>50.55</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3527,7 +3703,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>tr-c915e6367afa</t>
+          <t>tr-8c385d4c7dc2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3542,21 +3718,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.753</t>
+          <t>18:06:33.860</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.817</t>
+          <t>18:06:33.915</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>64.37</v>
+        <v>55.04</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3565,7 +3746,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>tr-91a0e8cd799d</t>
+          <t>tr-d97e451482a3</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3580,21 +3761,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.769</t>
+          <t>18:06:33.867</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.833</t>
+          <t>18:06:33.915</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>63.93</v>
+        <v>47.86</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3603,7 +3789,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>tr-2bab15709914</t>
+          <t>tr-48839901db66</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3618,21 +3804,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.769</t>
+          <t>18:06:33.874</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.832</t>
+          <t>18:06:33.924</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>62.6</v>
+        <v>49.97</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3641,7 +3832,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>tr-4605e174dff6</t>
+          <t>tr-4dc4136e1702</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3656,21 +3847,26 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.777</t>
+          <t>18:06:33.898</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.841</t>
+          <t>18:06:33.951</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>64.25</v>
+        <v>53.37</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3679,7 +3875,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>tr-607395d5a272</t>
+          <t>tr-c32a20c4dea1</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3694,21 +3890,26 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.787</t>
+          <t>18:06:33.898</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.846</t>
+          <t>18:06:33.950</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>58.32</v>
+        <v>51.98</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3717,7 +3918,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>tr-5de4061e982e</t>
+          <t>tr-2f5ef6e1e049</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3732,21 +3933,26 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.817</t>
+          <t>18:06:33.915</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.882</t>
+          <t>18:06:33.962</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>65.02</v>
+        <v>46.91</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3755,7 +3961,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>tr-715497e47a72</t>
+          <t>tr-6ffcd97b5416</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3770,21 +3976,26 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.832</t>
+          <t>18:06:33.915</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.908</t>
+          <t>18:06:33.968</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>75.86</v>
+        <v>53.53</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3793,7 +4004,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>tr-4b7941f7407b</t>
+          <t>tr-6fe92e4b52f7</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3808,21 +4019,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.833</t>
+          <t>18:06:33.924</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.902</t>
+          <t>18:06:33.974</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>69.28</v>
+        <v>50.24</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3831,7 +4047,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>tr-cebd7c85590b</t>
+          <t>tr-0535043e72a9</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3846,21 +4062,26 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.841</t>
+          <t>18:06:33.951</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.902</t>
+          <t>18:06:34.010</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>60.72</v>
+        <v>59</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3869,7 +4090,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>tr-f8199c9e0c6e</t>
+          <t>tr-9aa730c5762e</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3884,21 +4105,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.846</t>
+          <t>18:06:33.951</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.916</t>
+          <t>18:06:34.007</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>70.65000000000001</v>
+        <v>56</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3907,7 +4133,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>tr-0298b492bf26</t>
+          <t>tr-d72cda247024</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3922,21 +4148,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.882</t>
+          <t>18:06:33.962</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.952</t>
+          <t>18:06:34.017</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>69.81</v>
+        <v>54.69</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3945,7 +4176,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>tr-28300329faef</t>
+          <t>tr-57db876f1530</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3960,21 +4191,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.902</t>
+          <t>18:06:33.968</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>17:47:53.005</t>
+          <t>18:06:34.038</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>103.36</v>
+        <v>69.06</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3983,7 +4219,7 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>tr-9b717ca34752</t>
+          <t>tr-dd41d04f29e4</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3998,21 +4234,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.902</t>
+          <t>18:06:33.974</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.981</t>
+          <t>18:06:34.047</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>78.87</v>
+        <v>72.95</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4021,7 +4262,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>tr-4009137e5f7f</t>
+          <t>tr-df1fb8438fc0</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4036,21 +4277,26 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.909</t>
+          <t>18:06:34.007</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>17:47:53.018</t>
+          <t>18:06:34.102</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>108.47</v>
+        <v>94.97</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4059,7 +4305,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>tr-258c05c8248b</t>
+          <t>tr-1f2197bcf7d0</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4074,21 +4320,26 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.916</t>
+          <t>18:06:34.010</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17:47:53.017</t>
+          <t>18:06:34.114</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>100.42</v>
+        <v>104.2</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4097,7 +4348,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>tr-b3d3b48134e2</t>
+          <t>tr-530bec084d42</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4112,21 +4363,26 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>17:47:52.953</t>
+          <t>18:06:34.017</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>17:47:53.038</t>
+          <t>18:06:34.113</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>85.16</v>
+        <v>96.7</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
